--- a/Config/TalentEntryConfig.xlsx
+++ b/Config/TalentEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14010" windowHeight="10905"/>
+    <workbookView windowWidth="12315" windowHeight="11595"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="121">
   <si>
     <t>##var</t>
   </si>
@@ -85,7 +85,7 @@
     <t>TwoCardAttack</t>
   </si>
   <si>
-    <t>数字牌2提供的攻击力+1</t>
+    <t>数字牌2提供额外攻击力</t>
   </si>
   <si>
     <t>3点精通</t>
@@ -97,7 +97,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>数字牌3提供的攻击力+1</t>
+    <t>数字牌3提供额外攻击力</t>
   </si>
   <si>
     <t>4点精通</t>
@@ -106,7 +106,7 @@
     <t>FourCardAttack</t>
   </si>
   <si>
-    <t>数字牌4提供的攻击力+1</t>
+    <t>数字牌4提供额外攻击力</t>
   </si>
   <si>
     <t>5点精通</t>
@@ -115,7 +115,7 @@
     <t>FiveCardAttack</t>
   </si>
   <si>
-    <t>数字牌5提供的攻击力+1</t>
+    <t>数字牌5提供额外攻击力</t>
   </si>
   <si>
     <t>6点精通</t>
@@ -124,7 +124,7 @@
     <t>SixCardAttack</t>
   </si>
   <si>
-    <t>数字牌6提供的攻击力+1</t>
+    <t>数字牌6提供额外攻击力</t>
   </si>
   <si>
     <t>7点精通</t>
@@ -133,7 +133,7 @@
     <t>SevenCardAttack</t>
   </si>
   <si>
-    <t>数字牌7提供的攻击力+1</t>
+    <t>数字牌7提供额外攻击力</t>
   </si>
   <si>
     <t>8点精通</t>
@@ -142,7 +142,7 @@
     <t>EightCardAttack</t>
   </si>
   <si>
-    <t>数字牌8提供的攻击力+1</t>
+    <t>数字牌8提供额外攻击力</t>
   </si>
   <si>
     <t>9点精通</t>
@@ -151,7 +151,7 @@
     <t>NineCardAttack</t>
   </si>
   <si>
-    <t>数字牌9提供的攻击力+1</t>
+    <t>数字牌9提供额外攻击力</t>
   </si>
   <si>
     <t>10点精通</t>
@@ -160,40 +160,241 @@
     <t>TenCardAttack</t>
   </si>
   <si>
-    <t>数字牌10提供的攻击力+1</t>
+    <t>数字牌10提供额外攻击力</t>
   </si>
   <si>
     <t>结实</t>
   </si>
   <si>
-    <t>Sturdy</t>
+    <t>HeroHpMax</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>英雄的生命值上限+4</t>
+    <t>英雄的血量上限</t>
   </si>
   <si>
     <t>铜墙铁壁</t>
   </si>
   <si>
-    <t>ImpregnableFortress</t>
+    <t>HeroTakeDamage</t>
   </si>
   <si>
     <t>-1</t>
   </si>
   <si>
-    <t>受到的伤害降低1点</t>
+    <t>英雄承受的伤害</t>
   </si>
   <si>
     <t>强壮</t>
   </si>
   <si>
-    <t>Strong</t>
-  </si>
-  <si>
-    <t>英雄的基础攻击力+1</t>
+    <t>HeroAttack</t>
+  </si>
+  <si>
+    <t>英雄的基础攻击力</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>人头精通</t>
+  </si>
+  <si>
+    <t>HeadCardAttack</t>
+  </si>
+  <si>
+    <t>人头牌提供额外攻击力</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>强力打击</t>
+  </si>
+  <si>
+    <t>HeroCritical</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>英雄的暴击率</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>巨人杀手</t>
+  </si>
+  <si>
+    <t>AttackBossDamage</t>
+  </si>
+  <si>
+    <t>对BOSS的伤害提高</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>好兆头</t>
+  </si>
+  <si>
+    <t>FirstShowCardEveryLevel</t>
+  </si>
+  <si>
+    <t>0.2</t>
+  </si>
+  <si>
+    <t>每关首次亮牌倍率提高</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>侩子手</t>
+  </si>
+  <si>
+    <t>KillingProbabilityTen</t>
+  </si>
+  <si>
+    <t>斩杀10%血量以下的非BOSS敌人概率</t>
+  </si>
+  <si>
+    <t>206</t>
+  </si>
+  <si>
+    <t>逢凶化吉</t>
+  </si>
+  <si>
+    <t>KillingBringsBackBlood</t>
+  </si>
+  <si>
+    <t>血量低于20%以下时,杀人回血</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>人多势众</t>
+  </si>
+  <si>
+    <t>ManyMonsterDamage</t>
+  </si>
+  <si>
+    <t>敌人数量大于1时,伤害提高</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>搓牌高手</t>
+  </si>
+  <si>
+    <t>UsingRubbingCards</t>
+  </si>
+  <si>
+    <t>亮牌前使用过搓牌,结算攻击力提高</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>回复</t>
+  </si>
+  <si>
+    <t>HeroHpReplyEveryLevelEnding</t>
+  </si>
+  <si>
+    <t>每关结束后,回复血量</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>资本家</t>
+  </si>
+  <si>
+    <t>ProOfObtainingFundsEverySettlement</t>
+  </si>
+  <si>
+    <t>结算时,获得额外资金的概率</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>A点精通</t>
+  </si>
+  <si>
+    <t>ACardAttack</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>A牌提供的攻击力提高</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>孤立无援</t>
+  </si>
+  <si>
+    <t>OneMonsterDamage</t>
+  </si>
+  <si>
+    <t>只剩1名敌人时,伤害提高</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>触底反弹</t>
+  </si>
+  <si>
+    <t>HpUnderDamage</t>
+  </si>
+  <si>
+    <t>血量低于20%时,伤害提高</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>点金手</t>
+  </si>
+  <si>
+    <t>KillingProOfObtainingFunds</t>
+  </si>
+  <si>
+    <t>击杀敌人时,获得额外资金的概率</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>富裕</t>
+  </si>
+  <si>
+    <t>InitialFunds</t>
+  </si>
+  <si>
+    <t>初始拥有资金</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>追击</t>
+  </si>
+  <si>
+    <t>ProOfExtraAttack</t>
+  </si>
+  <si>
+    <t>额外造成1次10%伤害的概率</t>
   </si>
 </sst>
 </file>
@@ -1167,13 +1368,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="7.71666666666667" style="1" customWidth="1"/>
     <col min="3" max="3" width="9.34166666666667" style="2" customWidth="1"/>
-    <col min="4" max="4" width="19.4583333333333" style="2" customWidth="1"/>
+    <col min="4" max="4" width="27.8166666666667" style="2" customWidth="1"/>
     <col min="5" max="5" width="6.375" style="1" customWidth="1"/>
     <col min="6" max="6" width="21.4083333333333" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
@@ -1444,6 +1645,278 @@
         <v>53</v>
       </c>
     </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6">
+      <c r="B34" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/TalentEntryConfig.xlsx
+++ b/Config/TalentEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="12315" windowHeight="11595"/>
+    <workbookView windowWidth="14175" windowHeight="10740"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="134">
   <si>
     <t>##var</t>
   </si>
@@ -298,6 +298,21 @@
     <t>亮牌前使用过搓牌,结算攻击力提高</t>
   </si>
   <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>史诗圣物</t>
+  </si>
+  <si>
+    <t>EpicRelicPro</t>
+  </si>
+  <si>
+    <t>0.002</t>
+  </si>
+  <si>
+    <t>商店中出现史诗品质圣物的概率提高</t>
+  </si>
+  <si>
     <t>301</t>
   </si>
   <si>
@@ -395,6 +410,30 @@
   </si>
   <si>
     <t>额外造成1次10%伤害的概率</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>传说圣物</t>
+  </si>
+  <si>
+    <t>LegendRelicPro</t>
+  </si>
+  <si>
+    <t>商店中出现传说品质圣物的概率提高</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>圣物容量</t>
+  </si>
+  <si>
+    <t>RelicNumMax</t>
+  </si>
+  <si>
+    <t>允许携带的圣物容量提高</t>
   </si>
 </sst>
 </file>
@@ -1368,7 +1407,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -1781,52 +1820,52 @@
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="2:6">
-      <c r="B27" s="1" t="s">
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C26" t="s">
         <v>89</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="F27" s="1" t="s">
+      <c r="E26" s="1" t="s">
         <v>91</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>61</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>100</v>
@@ -1839,82 +1878,133 @@
       <c r="C30" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="2" t="s">
         <v>103</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>61</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>61</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E34" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F34" s="1" t="s">
-        <v>120</v>
+      <c r="F35" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6">
+      <c r="B36" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C36" t="s">
+        <v>127</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6">
+      <c r="B37" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C37" t="s">
+        <v>131</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/Config/TalentEntryConfig.xlsx
+++ b/Config/TalentEntryConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="14175" windowHeight="10740"/>
+    <workbookView windowWidth="16590" windowHeight="10440"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
